--- a/exports/colleges/26016_the-west-bengal-national-university-of-juridical-sciences-wbnujs-kolkata.xlsx
+++ b/exports/colleges/26016_the-west-bengal-national-university-of-juridical-sciences-wbnujs-kolkata.xlsx
@@ -445,7 +445,7 @@
     <col width="188" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
     <col width="25" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="156" customWidth="1" min="13" max="13"/>
@@ -570,7 +570,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>CD Rank #19</t>
+          <t>Rank #3</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -605,11 +605,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="78" customWidth="1" min="3" max="3"/>
     <col width="78" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
@@ -617,7 +617,7 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
     <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
   </cols>
@@ -692,7 +692,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BBA</t>
+          <t>Bachelor of Arts + Bachelor of Laws [BALLB] {Hons.}</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -702,17 +702,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Bachelor of Arts + Bachelor of Laws [BALLB] {Hons.}</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>16.8 Lakhs</t>
+          <t>16.8 L</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>5 Years</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>10+2 with CLAT</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>1 Jan - 16 Mar 2026</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -764,17 +764,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>M.Phil/Ph.D in Law</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.65 Lakhs</t>
+          <t>1.65 L</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>3 Years</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -784,12 +784,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Post Graduation with 55%</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CBSE UGC NET, AILET, ILICAT</t>
+          <t>GATE / UGC NET</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LLM</t>
+          <t>Master of Laws [L.L.M]</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -826,17 +826,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Master of Laws [L.L.M]</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.8 Lakhs</t>
+          <t>1.8 L</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1 Year</t>
+          <t>1 year</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -846,17 +846,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.L.B. with CLAT</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CLAT PG</t>
+          <t>CLAT</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>1 Jan - 16 Mar 2026</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>Doctorate of Law [L.L.D]</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -888,17 +888,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Doctorate of Law [L.L.D]</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.65 Lakhs</t>
+          <t>1.65 L</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>3 Years</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AILET, ILICAT</t>
+          <t>GATE / UGC NET</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LLB</t>
+          <t>B.Sc</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -955,12 +955,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>21.4 Lakhs</t>
+          <t>21.4 L</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>5 Years</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -970,17 +970,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>10+2 with CLAT</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CLAT</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>1 Aug - 31 Oct 2026</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1002,27 +1002,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>Certificate in Computer Forensics and Cyber Crime</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BALLB {Hons.}</t>
+          <t>Certificate in Computer Forensics and Cyber Crime</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>BALLB {Hons.}</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>16.8 Lakhs</t>
+          <t>20,000</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>3 Years</t>
+          <t>1 year</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>29 Sept - 31 Oct 2026</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1064,27 +1064,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>L.L.M</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>L.L.M</t>
+          <t>Master of Science [M.Sc]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>L.L.M</t>
+          <t>Master of Science [M.Sc]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.8 Lakhs</t>
+          <t>2.22 L - 2.7 L</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1099,12 +1099,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>IIT JAM</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>1 Jan - 16 Mar 2026</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1126,27 +1126,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>M.A. (Criminology &amp; Criminal Justice)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>M.A. (Criminology &amp; Criminal Justice)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.65 Lakhs</t>
+          <t>2.22 L</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>3-5 Years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>GATE / UGC NET</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>1 Jan - 16 Mar 2026</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Doctorate</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1188,27 +1188,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>B.Sc</t>
+          <t>BBA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B.Sc + L.L.B {Hons.}</t>
+          <t>Bachelor of Arts + Bachelor of Laws [BALLB] {Hons.}</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>B.Sc + L.L.B {Hons.}</t>
+          <t>Bachelor of Arts + Bachelor of Laws [BALLB] {Hons.}</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>21.4 Lakhs</t>
+          <t>16.8 Lakhs</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>3 Years</t>
+          <t>5 Years</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>10+2 with CLAT</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>CLAT</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1250,27 +1250,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Certification</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Certification</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Certification</t>
+          <t>M.Phil/Ph.D in Law</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>1.65 Lakhs</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3 Years</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1280,12 +1280,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Post Graduation with 55%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>CBSE UGC NET, AILET, ILICAT</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -1312,27 +1312,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>Master of Laws [L.L.M]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>Master of Laws [L.L.M]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2.22 Lakhs - 2.7 Lakhs</t>
+          <t>1.8 Lakhs</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>1 Year</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1342,12 +1342,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>L.L.B. with CLAT</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>CLAT PG</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1374,27 +1374,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>M.A</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>M.A</t>
+          <t>Doctorate of Law [L.L.D]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>M.A</t>
+          <t>Doctorate of Law [L.L.D]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2.22 Lakhs</t>
+          <t>1.65 Lakhs</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3 Years</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1404,12 +1404,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>AILET, ILICAT</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -1436,27 +1436,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>L.L.M Criminal And Security Law</t>
+          <t>LLB</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>L.L.M Criminal And Security Law</t>
+          <t>Bachelor of Science + Bachelor of Laws [B.Sc L.L.B.] {Hons.} (Forensic Law)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>L.L.M Criminal And Security Law</t>
+          <t>Bachelor of Science + Bachelor of Laws [B.Sc L.L.B.] {Hons.} (Forensic Law)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.8 Lakhs</t>
+          <t>21.4 Lakhs</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>3-5 Years</t>
+          <t>5 Years</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>10+2 with CLAT</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1498,22 +1498,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>L.L.M Corporate And Commercial Law</t>
+          <t>BALLB {Hons.}</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>L.L.M Corporate And Commercial Law</t>
+          <t>BALLB {Hons.}</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>L.L.M Corporate And Commercial Law</t>
+          <t>BALLB {Hons.}</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.8 Lakhs</t>
+          <t>16.8 Lakhs</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1560,17 +1560,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>L.L.M International and Comparative Law</t>
+          <t>L.L.M</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>L.L.M International and Comparative Law</t>
+          <t>L.L.M</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>L.L.M International and Comparative Law</t>
+          <t>L.L.M</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>3-5 Years</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>CLAT</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1622,22 +1622,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>L.L.M Intellectual Property &amp; Business Law</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>L.L.M Intellectual Property &amp; Business Law</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>L.L.M Intellectual Property &amp; Business Law</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.8 Lakhs</t>
+          <t>1.65 Lakhs</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>CLAT</t>
+          <t>GATE / UGC NET</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -1684,27 +1684,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>L.L.M Technology Law</t>
+          <t>B.Sc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>L.L.M Technology Law</t>
+          <t>B.Sc + L.L.B {Hons.}</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>L.L.M Technology Law</t>
+          <t>B.Sc + L.L.B {Hons.}</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.8 Lakhs</t>
+          <t>21.4 Lakhs</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>3-5 Years</t>
+          <t>3 Years</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CLAT</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1746,27 +1746,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>Certification</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ph.D Law</t>
+          <t>Certification</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Ph.D Law</t>
+          <t>Certification</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.65 Lakhs</t>
+          <t>20,000</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>3-5 Years</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>GATE / UGC NET</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Doctorate</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -1808,27 +1808,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ph.D Forensic Science</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Ph.D Forensic Science</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.65 Lakhs</t>
+          <t>2.22 Lakhs - 2.7 Lakhs</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>3-5 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>GATE / UGC NET</t>
+          <t>IIT JAM</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Doctorate</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1870,27 +1870,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>M.A</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ph.D Economics</t>
+          <t>M.A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Ph.D Economics</t>
+          <t>M.A</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.65 Lakhs</t>
+          <t>2.22 Lakhs</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>3-5 Years</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>GATE / UGC NET</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Doctorate</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -1932,22 +1932,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>L.L.M Criminal And Security Law</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ph.D History</t>
+          <t>L.L.M Criminal And Security Law</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Ph.D History</t>
+          <t>L.L.M Criminal And Security Law</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.65 Lakhs</t>
+          <t>1.8 Lakhs</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>GATE / UGC NET</t>
+          <t>CLAT</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Doctorate</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -1994,22 +1994,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>L.L.M Corporate And Commercial Law</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ph.D Political Science</t>
+          <t>L.L.M Corporate And Commercial Law</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Ph.D Political Science</t>
+          <t>L.L.M Corporate And Commercial Law</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.65 Lakhs</t>
+          <t>1.8 Lakhs</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>GATE / UGC NET</t>
+          <t>CLAT</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Doctorate</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -2056,25 +2056,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>B.Sc + L.L.B {Hons.}</t>
+          <t>L.L.M International and Comparative Law</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B.Sc + L.L.B {Hons.} (General)</t>
+          <t>L.L.M International and Comparative Law</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>L.L.M International and Comparative Law</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>21.4 Lakhs</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
+          <t>1.8 Lakhs</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>3-5 Years</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>Full Time</t>
@@ -2087,7 +2091,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>CLAT</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2114,25 +2118,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Certification</t>
+          <t>L.L.M Intellectual Property &amp; Business Law</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Certification (General)</t>
+          <t>L.L.M Intellectual Property &amp; Business Law</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>L.L.M Intellectual Property &amp; Business Law</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>20,000</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
+          <t>1.8 Lakhs</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>3-5 Years</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>Full Time</t>
@@ -2145,7 +2153,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>CLAT</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2172,25 +2180,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>L.L.M Technology Law</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>M.Sc (General)</t>
+          <t>L.L.M Technology Law</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>L.L.M Technology Law</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2.22 Lakhs - 2.7 Lakhs</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
+          <t>1.8 Lakhs</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>3-5 Years</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
           <t>Full Time</t>
@@ -2203,7 +2215,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>CLAT</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2230,51 +2242,535 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>Ph.D</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ph.D Law</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Ph.D Law</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1.65 Lakhs</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>3-5 Years</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>GATE / UGC NET</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Doctorate</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>26016</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Ph.D</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ph.D Forensic Science</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Ph.D Forensic Science</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1.65 Lakhs</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>3-5 Years</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>GATE / UGC NET</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Doctorate</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>26016</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Ph.D</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ph.D Economics</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Ph.D Economics</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1.65 Lakhs</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>3-5 Years</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>GATE / UGC NET</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Doctorate</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>26016</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Ph.D</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ph.D History</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Ph.D History</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1.65 Lakhs</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>3-5 Years</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>GATE / UGC NET</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Doctorate</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>26016</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Ph.D</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ph.D Political Science</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Ph.D Political Science</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1.65 Lakhs</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>3-5 Years</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>GATE / UGC NET</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Doctorate</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>26016</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>B.Sc + L.L.B {Hons.}</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>B.Sc + L.L.B {Hons.} (General)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>21.4 Lakhs</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>26016</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Certification</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Certification (General)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>26016</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>M.Sc</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>M.Sc (General)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2.22 Lakhs - 2.7 Lakhs</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>26016</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
           <t>M.A</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>M.A (General)</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>2.22 Lakhs</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t>UG</t>
         </is>
@@ -2428,7 +2924,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>22,00,000</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2463,13 +2959,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2480,17 +2974,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>ranking_body</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>rank</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>ranking_year</t>
+          <t>status</t>
         </is>
       </c>
     </row>
@@ -2502,15 +2986,9 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Collegedunia</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>CD Rank #19</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>No Data Available</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
